--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2018/NEW_YORK_2018.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2018/NEW_YORK_2018.xlsx
@@ -3271,7 +3271,7 @@
         <v>24</v>
       </c>
       <c r="D162">
-        <v>0.0009302325581395349</v>
+        <v>0.0009302325581395348</v>
       </c>
     </row>
     <row r="163">
@@ -3397,7 +3397,7 @@
         <v>243</v>
       </c>
       <c r="D169">
-        <v>0.009418604651162791</v>
+        <v>0.009418604651162793</v>
       </c>
     </row>
     <row r="170">
@@ -4380,7 +4380,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C224">
@@ -11191,7 +11191,7 @@
         <v>25</v>
       </c>
       <c r="D602">
-        <v>0.0009689922480620155</v>
+        <v>0.0009689922480620156</v>
       </c>
     </row>
     <row r="603">
@@ -12300,7 +12300,7 @@
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C664">
@@ -12318,7 +12318,7 @@
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C665">
@@ -12685,7 +12685,7 @@
         <v>24</v>
       </c>
       <c r="D685">
-        <v>0.0009302325581395349</v>
+        <v>0.0009302325581395348</v>
       </c>
     </row>
     <row r="686">
@@ -13308,7 +13308,7 @@
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C720">
@@ -15349,7 +15349,7 @@
         <v>25</v>
       </c>
       <c r="D833">
-        <v>0.0009689922480620155</v>
+        <v>0.0009689922480620156</v>
       </c>
     </row>
     <row r="834">
@@ -16501,7 +16501,7 @@
         <v>246</v>
       </c>
       <c r="D897">
-        <v>0.009534883720930233</v>
+        <v>0.009534883720930231</v>
       </c>
     </row>
     <row r="898">
@@ -18949,7 +18949,7 @@
         <v>24</v>
       </c>
       <c r="D1033">
-        <v>0.0009302325581395349</v>
+        <v>0.0009302325581395348</v>
       </c>
     </row>
     <row r="1034">
@@ -19147,7 +19147,7 @@
         <v>25</v>
       </c>
       <c r="D1044">
-        <v>0.0009689922480620155</v>
+        <v>0.0009689922480620156</v>
       </c>
     </row>
     <row r="1045">
@@ -21127,7 +21127,7 @@
         <v>25</v>
       </c>
       <c r="D1154">
-        <v>0.0009689922480620155</v>
+        <v>0.0009689922480620156</v>
       </c>
     </row>
     <row r="1155">
@@ -21541,7 +21541,7 @@
         <v>25</v>
       </c>
       <c r="D1177">
-        <v>0.0009689922480620155</v>
+        <v>0.0009689922480620156</v>
       </c>
     </row>
     <row r="1178">
@@ -21786,7 +21786,7 @@
       </c>
       <c r="B1191" t="inlineStr">
         <is>
-          <t>Ziltlaltepec De Trinidad Sanchez Santos</t>
+          <t>Zitlaltepec De Trinidad Sanchez Santos</t>
         </is>
       </c>
       <c r="C1191">
@@ -22387,7 +22387,7 @@
         <v>25</v>
       </c>
       <c r="D1224">
-        <v>0.0009689922480620155</v>
+        <v>0.0009689922480620156</v>
       </c>
     </row>
     <row r="1225">
